--- a/ReporteVendedores.xlsx
+++ b/ReporteVendedores.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>REPORTE DE VENDEDORES</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Tipo de pago</t>
   </si>
   <si>
     <t>GANANCIA POR VENDEDOR</t>
@@ -88,14 +91,14 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="18"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
+      <sz val="18"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
@@ -703,20 +706,22 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1089,16 +1094,16 @@
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="N1" s="9"/>
+      <c r="O1" s="9"/>
+      <c r="P1" s="9"/>
+      <c r="Q1" s="9"/>
+      <c r="R1" s="9"/>
     </row>
     <row r="2" customHeight="1" spans="1:18">
       <c r="A2" s="1"/>
@@ -1106,16 +1111,16 @@
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="3"/>
-      <c r="Q2" s="3"/>
-      <c r="R2" s="3"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="3"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
     </row>
     <row r="3" customHeight="1" spans="1:18">
       <c r="A3" s="1"/>
@@ -1123,16 +1128,16 @@
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
-      <c r="P3" s="3"/>
-      <c r="Q3" s="3"/>
-      <c r="R3" s="3"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="9"/>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
     </row>
     <row r="4" customHeight="1" spans="1:18">
       <c r="A4" s="1"/>
@@ -1140,52 +1145,52 @@
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="N4" s="3"/>
-      <c r="O4" s="3"/>
-      <c r="P4" s="3"/>
-      <c r="Q4" s="3"/>
-      <c r="R4" s="3"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9"/>
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9"/>
     </row>
     <row r="5" customHeight="1" spans="1:18">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
-      <c r="P5" s="3"/>
-      <c r="Q5" s="3"/>
-      <c r="R5" s="3"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
     </row>
     <row r="6" ht="23.25" customHeight="1" spans="1:18">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="5"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="6"/>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="N6" s="6"/>
-      <c r="O6" s="6"/>
-      <c r="P6" s="6"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="6"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+      <c r="Q6" s="10"/>
+      <c r="R6" s="10"/>
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:10">
       <c r="A7" s="7" t="s">
@@ -1203,7 +1208,9 @@
       <c r="E7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="7"/>
+      <c r="F7" s="7" t="s">
+        <v>7</v>
+      </c>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
       <c r="I7" s="7"/>
@@ -1219,11 +1226,11 @@
         <f>IF(H8&gt;=4000,IF(AND(H8&gt;=4000,H8&gt;=8000),"Bono +$200","Bono +$100"),"")</f>
         <v/>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="3"/>
-      <c r="P8" s="3"/>
-      <c r="Q8" s="3"/>
-      <c r="R8" s="3"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9"/>
+      <c r="Q8" s="9"/>
+      <c r="R8" s="9"/>
     </row>
     <row r="9" customHeight="1" spans="8:18">
       <c r="H9" s="8"/>
@@ -1235,11 +1242,11 @@
         <f t="shared" ref="K9:K72" si="1">IF(H9&gt;=4000,IF(AND(H9&gt;=4000,H9&gt;=8000),"Bono +$200","Bono +$100"),"")</f>
         <v/>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="3"/>
-      <c r="P9" s="3"/>
-      <c r="Q9" s="3"/>
-      <c r="R9" s="3"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9"/>
+      <c r="Q9" s="9"/>
+      <c r="R9" s="9"/>
     </row>
     <row r="10" customHeight="1" spans="8:18">
       <c r="H10" s="8"/>
@@ -1251,11 +1258,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="3"/>
-      <c r="P10" s="3"/>
-      <c r="Q10" s="3"/>
-      <c r="R10" s="3"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9"/>
+      <c r="Q10" s="9"/>
+      <c r="R10" s="9"/>
     </row>
     <row r="11" customHeight="1" spans="8:18">
       <c r="H11" s="8"/>
@@ -1267,11 +1274,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
-      <c r="P11" s="3"/>
-      <c r="Q11" s="3"/>
-      <c r="R11" s="3"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="9"/>
+      <c r="P11" s="9"/>
+      <c r="Q11" s="9"/>
+      <c r="R11" s="9"/>
     </row>
     <row r="12" customHeight="1" spans="8:18">
       <c r="H12" s="8"/>
@@ -1283,11 +1290,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="3"/>
-      <c r="P12" s="3"/>
-      <c r="Q12" s="3"/>
-      <c r="R12" s="3"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="9"/>
+      <c r="P12" s="9"/>
+      <c r="Q12" s="9"/>
+      <c r="R12" s="9"/>
     </row>
     <row r="13" customHeight="1" spans="8:18">
       <c r="H13" s="8"/>
@@ -1299,11 +1306,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="3"/>
-      <c r="P13" s="3"/>
-      <c r="Q13" s="3"/>
-      <c r="R13" s="3"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="9"/>
+      <c r="P13" s="9"/>
+      <c r="Q13" s="9"/>
+      <c r="R13" s="9"/>
     </row>
     <row r="14" ht="23.25" customHeight="1" spans="8:18">
       <c r="H14" s="8"/>
@@ -1315,11 +1322,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N14" s="6"/>
-      <c r="O14" s="6"/>
-      <c r="P14" s="6"/>
-      <c r="Q14" s="6"/>
-      <c r="R14" s="6"/>
+      <c r="N14" s="10"/>
+      <c r="O14" s="10"/>
+      <c r="P14" s="10"/>
+      <c r="Q14" s="10"/>
+      <c r="R14" s="10"/>
     </row>
     <row r="15" spans="8:11">
       <c r="H15" s="8"/>
@@ -1342,11 +1349,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3"/>
-      <c r="R16" s="3"/>
+      <c r="N16" s="9"/>
+      <c r="O16" s="9"/>
+      <c r="P16" s="9"/>
+      <c r="Q16" s="9"/>
+      <c r="R16" s="9"/>
     </row>
     <row r="17" customHeight="1" spans="8:18">
       <c r="H17" s="8"/>
@@ -1358,11 +1365,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="3"/>
-      <c r="P17" s="3"/>
-      <c r="Q17" s="3"/>
-      <c r="R17" s="3"/>
+      <c r="N17" s="9"/>
+      <c r="O17" s="9"/>
+      <c r="P17" s="9"/>
+      <c r="Q17" s="9"/>
+      <c r="R17" s="9"/>
     </row>
     <row r="18" customHeight="1" spans="8:18">
       <c r="H18" s="8"/>
@@ -1374,11 +1381,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="3"/>
-      <c r="R18" s="3"/>
+      <c r="N18" s="9"/>
+      <c r="O18" s="9"/>
+      <c r="P18" s="9"/>
+      <c r="Q18" s="9"/>
+      <c r="R18" s="9"/>
     </row>
     <row r="19" customHeight="1" spans="8:18">
       <c r="H19" s="8"/>
@@ -1390,11 +1397,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
-      <c r="P19" s="3"/>
-      <c r="Q19" s="3"/>
-      <c r="R19" s="3"/>
+      <c r="N19" s="9"/>
+      <c r="O19" s="9"/>
+      <c r="P19" s="9"/>
+      <c r="Q19" s="9"/>
+      <c r="R19" s="9"/>
     </row>
     <row r="20" customHeight="1" spans="8:18">
       <c r="H20" s="8"/>
@@ -1406,11 +1413,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3"/>
-      <c r="R20" s="3"/>
+      <c r="N20" s="9"/>
+      <c r="O20" s="9"/>
+      <c r="P20" s="9"/>
+      <c r="Q20" s="9"/>
+      <c r="R20" s="9"/>
     </row>
     <row r="21" customHeight="1" spans="8:18">
       <c r="H21" s="8"/>
@@ -1422,11 +1429,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
-      <c r="P21" s="3"/>
-      <c r="Q21" s="3"/>
-      <c r="R21" s="3"/>
+      <c r="N21" s="9"/>
+      <c r="O21" s="9"/>
+      <c r="P21" s="9"/>
+      <c r="Q21" s="9"/>
+      <c r="R21" s="9"/>
     </row>
     <row r="22" ht="23.25" customHeight="1" spans="8:18">
       <c r="H22" s="8"/>
@@ -1438,11 +1445,11 @@
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="6"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
-      <c r="R22" s="6"/>
+      <c r="N22" s="10"/>
+      <c r="O22" s="10"/>
+      <c r="P22" s="10"/>
+      <c r="Q22" s="10"/>
+      <c r="R22" s="10"/>
     </row>
     <row r="23" spans="8:11">
       <c r="H23" s="8"/>
@@ -18547,8 +18554,8 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertRows="0" insertColumns="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="2">
-    <mergeCell ref="A6:E6"/>
-    <mergeCell ref="A1:E5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A1:F4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait"/>
@@ -18571,7 +18578,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
